--- a/Nado Game/pyqt5/감면자료/data/xperp_code_comparasion_table.xlsx
+++ b/Nado Game/pyqt5/감면자료/data/xperp_code_comparasion_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\과장\1 1 부과자료\2024년\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pygame\Nado Game\pyqt5\감면자료\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A69D90-5FDD-43B5-9C3D-2F9EF9DE17DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320A207B-E660-4FA1-818B-7D56413B729D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-525" yWindow="2355" windowWidth="24705" windowHeight="14415" xr2:uid="{F4287AED-E29A-4F26-A7DC-1752CBD1210B}"/>
+    <workbookView xWindow="30210" yWindow="5580" windowWidth="19845" windowHeight="11910" xr2:uid="{F4287AED-E29A-4F26-A7DC-1752CBD1210B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="81">
   <si>
     <t>XPERP 전기 및 수도 감면 코드 비교표</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -170,18 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>복지개별</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>중증장애인감면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>독립유공자감면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>sheet name or field name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -344,6 +332,21 @@
   <si>
     <t>xperp 생명유지</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복지감면1 (독립유공자)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복지감면2 (기초생활수급자)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>복지감면3 (중증장애인)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>다자녀감면</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -490,6 +493,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -809,22 +815,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.75" customWidth="1"/>
+    <col min="1" max="1" width="7.69921875" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="5.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.09765625" customWidth="1"/>
+    <col min="6" max="6" width="5.19921875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="3" customWidth="1"/>
     <col min="8" max="8" width="25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="11" max="11" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -837,7 +843,7 @@
       <c r="H1" s="9"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -853,14 +859,14 @@
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="2" t="s">
@@ -878,10 +884,10 @@
       <c r="G3" s="11"/>
       <c r="H3" s="8"/>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>6</v>
@@ -890,7 +896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -901,7 +907,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>10</v>
@@ -910,7 +916,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" t="str">
@@ -930,7 +936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8"/>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -939,7 +945,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>11</v>
@@ -948,7 +954,7 @@
         <v>27</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" t="str">
@@ -968,7 +974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -977,7 +983,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>12</v>
@@ -986,7 +992,7 @@
         <v>15</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" t="str">
@@ -1006,28 +1012,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F7" s="2">
         <v>8</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="1"/>
@@ -1046,14 +1052,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>10</v>
@@ -1062,7 +1068,7 @@
         <v>24</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" t="str">
@@ -1082,7 +1088,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8"/>
       <c r="B9" s="1" t="s">
         <v>14</v>
@@ -1100,7 +1106,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" t="str">
@@ -1120,7 +1126,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8"/>
       <c r="B10" s="1" t="s">
         <v>14</v>
@@ -1138,7 +1144,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" t="str">
@@ -1158,7 +1164,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8"/>
       <c r="B11" s="1" t="s">
         <v>14</v>
@@ -1194,7 +1200,7 @@
         <v>C</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8"/>
       <c r="B12" s="1" t="s">
         <v>14</v>
@@ -1212,7 +1218,7 @@
         <v>2</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" t="str">
@@ -1232,28 +1238,28 @@
         <v>D</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8"/>
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2">
         <v>7</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
@@ -1272,13 +1278,13 @@
         <v>E</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8"/>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>28</v>
@@ -1290,10 +1296,10 @@
         <v>4</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="1"/>
@@ -1312,28 +1318,28 @@
         <v>G</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8"/>
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="1"/>
@@ -1352,7 +1358,7 @@
         <v>H</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8"/>
       <c r="B16" s="1" t="s">
         <v>14</v>
@@ -1370,10 +1376,10 @@
         <v>9</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="1"/>
@@ -1392,7 +1398,7 @@
         <v>I</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8"/>
       <c r="B17" s="1" t="s">
         <v>14</v>
@@ -1401,7 +1407,7 @@
         <v>21</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>23</v>
@@ -1411,7 +1417,7 @@
         <v>23</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" si="1"/>
@@ -1430,21 +1436,21 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8"/>
       <c r="B18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" t="str">
@@ -1464,23 +1470,23 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8"/>
       <c r="B19" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" t="str">
@@ -1500,7 +1506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8"/>
       <c r="B20" s="1" t="s">
         <v>14</v>
@@ -1509,7 +1515,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="2"/>
@@ -1532,26 +1538,26 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>78</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I21" t="str">
         <f>+$A$21</f>
@@ -1570,10 +1576,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8"/>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>12</v>
@@ -1581,13 +1587,13 @@
       <c r="D22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>12</v>
+      <c r="E22" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" ref="I22:I25" si="5">+$A$21</f>
@@ -1606,24 +1612,24 @@
         <v>I</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8"/>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" si="5"/>
@@ -1642,24 +1648,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="8"/>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>36</v>
+        <v>59</v>
+      </c>
+      <c r="E24" t="s">
+        <v>79</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" si="5"/>
@@ -1678,13 +1684,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="8"/>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>33</v>
@@ -1710,9 +1716,9 @@
         <v>V</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="60.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
@@ -1744,15 +1750,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DBB59CB-1095-45CD-851C-895890488597}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.25" customWidth="1"/>
-    <col min="2" max="2" width="9.75" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="1" max="1" width="10.19921875" customWidth="1"/>
+    <col min="2" max="2" width="9.69921875" customWidth="1"/>
+    <col min="3" max="3" width="27.19921875" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="str">
         <f>+Sheet1!I3</f>
         <v>종별</v>
@@ -1770,7 +1776,7 @@
         <v>코드</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="str">
         <f>+Sheet1!I4</f>
         <v>전기</v>
@@ -1788,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="str">
         <f>+Sheet1!I5</f>
         <v>전기</v>
@@ -1806,7 +1812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="str">
         <f>+Sheet1!I6</f>
         <v>전기</v>
@@ -1824,7 +1830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="str">
         <f>+Sheet1!I7</f>
         <v>전기</v>
@@ -1842,7 +1848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="str">
         <f>+Sheet1!I8</f>
         <v>전기</v>
@@ -1860,7 +1866,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="str">
         <f>+Sheet1!I9</f>
         <v>전기</v>
@@ -1878,7 +1884,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="str">
         <f>+Sheet1!I10</f>
         <v>전기</v>
@@ -1896,7 +1902,7 @@
         <v>B</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="str">
         <f>+Sheet1!I11</f>
         <v>전기</v>
@@ -1914,7 +1920,7 @@
         <v>C</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="str">
         <f>+Sheet1!I12</f>
         <v>전기</v>
@@ -1932,7 +1938,7 @@
         <v>D</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="str">
         <f>+Sheet1!I13</f>
         <v>전기</v>
@@ -1950,7 +1956,7 @@
         <v>E</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="str">
         <f>+Sheet1!I14</f>
         <v>전기</v>
@@ -1968,7 +1974,7 @@
         <v>G</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="str">
         <f>+Sheet1!I15</f>
         <v>전기</v>
@@ -1986,7 +1992,7 @@
         <v>H</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="str">
         <f>+Sheet1!I16</f>
         <v>전기</v>
@@ -2004,7 +2010,7 @@
         <v>I</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="str">
         <f>+Sheet1!I17</f>
         <v>전기</v>
@@ -2022,7 +2028,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="str">
         <f>+Sheet1!I18</f>
         <v>전기</v>
@@ -2040,7 +2046,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="str">
         <f>+Sheet1!I19</f>
         <v>전기</v>
@@ -2058,7 +2064,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="str">
         <f>+Sheet1!I20</f>
         <v>전기</v>
@@ -2076,7 +2082,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="str">
         <f>+Sheet1!I21</f>
         <v>수도</v>
@@ -2094,7 +2100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="str">
         <f>+Sheet1!I22</f>
         <v>수도</v>
@@ -2112,7 +2118,7 @@
         <v>I</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="str">
         <f>+Sheet1!I23</f>
         <v>수도</v>
@@ -2130,7 +2136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="str">
         <f>+Sheet1!I24</f>
         <v>수도</v>
@@ -2148,7 +2154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="str">
         <f>+Sheet1!I25</f>
         <v>수도</v>
@@ -2166,13 +2172,13 @@
         <v>V</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="1:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
